--- a/StructureDefinition-openelis-diagnostic-report.xlsx
+++ b/StructureDefinition-openelis-diagnostic-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T18:31:44+00:00</t>
+    <t>2025-09-03T10:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-diagnostic-report.xlsx
+++ b/StructureDefinition-openelis-diagnostic-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T10:18:48+00:00</t>
+    <t>2026-03-23T16:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -368,7 +368,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -619,7 +619,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -646,7 +646,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/analysisResult_uuid</t>
+    <t>http://openelis-global.org/analysisResult_uuid</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -719,7 +719,7 @@
     <t>DiagnosticReport.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -828,7 +828,7 @@
     <t>Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -856,7 +856,7 @@
     <t>Codes that describe Diagnostic Reports.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/report-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/report-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -971,7 +971,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1073,7 +1073,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1180,7 +1180,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy)
+    <t xml:space="preserve">Reference(ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -1263,7 +1263,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(Media|4.0.1)
 </t>
   </si>
   <si>
@@ -1310,7 +1310,7 @@
     <t>Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
@@ -1655,7 +1655,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.90625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-openelis-diagnostic-report.xlsx
+++ b/StructureDefinition-openelis-diagnostic-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:02:58+00:00</t>
+    <t>2026-05-11T11:15:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-diagnostic-report.xlsx
+++ b/StructureDefinition-openelis-diagnostic-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:15:58+00:00</t>
+    <t>2026-05-11T15:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-diagnostic-report.xlsx
+++ b/StructureDefinition-openelis-diagnostic-report.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:58:07+00:00</t>
+    <t>2026-05-12T16:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
